--- a/data/trans_orig/P37B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023</t>
+          <t>Población según el motivo por el que NO se vacunaron de la gripe en 2023 (tasa de respuesta: 97,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34275</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52338</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54450</t>
+          <t>53782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81190</t>
+          <t>81220</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17666</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43093</t>
+          <t>44723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150618</t>
+          <t>150273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176850</t>
+          <t>177381</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160746</t>
+          <t>158190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186836</t>
+          <t>186508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319386</t>
+          <t>320841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358218</t>
+          <t>359854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34964</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>10533</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51455</t>
+          <t>52515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157502</t>
+          <t>156349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>879624</t>
+          <t>890075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100215</t>
+          <t>99805</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151191</t>
+          <t>146983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275938</t>
+          <t>277854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1174553</t>
+          <t>1151959</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20198</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47464</t>
+          <t>48505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>19951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41698</t>
+          <t>41088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46365</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81715</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>753312</t>
+          <t>737956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1388872</t>
+          <t>1389561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1143193</t>
+          <t>1138209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1222285</t>
+          <t>1225777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1770076</t>
+          <t>1788021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2570670</t>
+          <t>2565518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73446</t>
+          <t>74490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>152936</t>
+          <t>150982</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109671</t>
+          <t>109086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156857</t>
+          <t>156753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189284</t>
+          <t>191864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290874</t>
+          <t>289777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60432</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54011</t>
+          <t>55781</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68702</t>
+          <t>71616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>105542</t>
+          <t>108344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>913</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62204</t>
+          <t>62453</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18466</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28231</t>
+          <t>28329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77433</t>
+          <t>73850</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>293652</t>
+          <t>295516</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>344615</t>
+          <t>343833</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>344367</t>
+          <t>342861</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>372870</t>
+          <t>369523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>653224</t>
+          <t>649490</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>707746</t>
+          <t>704002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37255</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20567</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41590</t>
+          <t>40605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>68122</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>223365</t>
+          <t>224645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>939906</t>
+          <t>1036912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,82 +2791,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>210887</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>183237</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>241175</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>666881</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>427809</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1339538</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>210887</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>183616</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>238946</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>666881</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>428845</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>1524001</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>12809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27866</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36235</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51178</t>
+          <t>51602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>103592</t>
+          <t>107771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45142</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80192</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>103203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>166342</t>
+          <t>165848</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1244934</t>
+          <t>1160705</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1884325</t>
+          <t>1877281</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1662880</t>
+          <t>1663641</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1754604</t>
+          <t>1757144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2654726</t>
+          <t>2778103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3598696</t>
+          <t>3595914</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118878</t>
+          <t>114684</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>203754</t>
+          <t>197182</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>153308</t>
+          <t>154327</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204611</t>
+          <t>206361</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284711</t>
+          <t>284834</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>385227</t>
+          <t>386958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P37B_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>32348</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>45446</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>55564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>77794</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>63233</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81220</t>
+          <t>93824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>11860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>20115</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39507</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>23537</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>15760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44723</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>164773</t>
+          <t>196625</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150273</t>
+          <t>180440</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177381</t>
+          <t>211993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>175409</t>
+          <t>198686</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158190</t>
+          <t>186805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186508</t>
+          <t>210865</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>340181</t>
+          <t>395311</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320841</t>
+          <t>375496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>359854</t>
+          <t>413357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34913</t>
+          <t>35747</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>11681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>42946</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>33095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52515</t>
+          <t>54861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>226475</t>
+          <t>268999</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>226475</t>
+          <t>268999</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>226475</t>
+          <t>268999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253144</t>
+          <t>277922</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253144</t>
+          <t>277922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253144</t>
+          <t>277922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>479618</t>
+          <t>546921</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>479618</t>
+          <t>546921</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>479618</t>
+          <t>546921</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>387192</t>
+          <t>149026</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156349</t>
+          <t>120605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>890075</t>
+          <t>178646</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>125354</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99805</t>
+          <t>130249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146983</t>
+          <t>176846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>512546</t>
+          <t>299703</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277854</t>
+          <t>263911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1151959</t>
+          <t>339717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>21881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>40961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>45561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>32273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48505</t>
+          <t>62094</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>29960</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>45272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>78599</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45428</t>
+          <t>62964</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81034</t>
+          <t>98437</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1183419</t>
+          <t>1292415</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>737956</t>
+          <t>1256164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1389561</t>
+          <t>1330637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1172266</t>
+          <t>1207691</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1138209</t>
+          <t>1175259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1225777</t>
+          <t>1238817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2355685</t>
+          <t>2500106</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1788021</t>
+          <t>2450313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2565518</t>
+          <t>2546517</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>117226</t>
+          <t>120968</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74490</t>
+          <t>98128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150982</t>
+          <t>149318</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>133278</t>
+          <t>145580</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109086</t>
+          <t>126252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156753</t>
+          <t>167924</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>250504</t>
+          <t>266547</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>191864</t>
+          <t>238390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289777</t>
+          <t>303255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1724519</t>
+          <t>1617286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1724519</t>
+          <t>1617286</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1724519</t>
+          <t>1617286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1473744</t>
+          <t>1551359</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1473744</t>
+          <t>1551359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1473744</t>
+          <t>1551359</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3198263</t>
+          <t>3168645</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3198263</t>
+          <t>3168645</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3198263</t>
+          <t>3168645</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44572</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60660</t>
+          <t>69273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33694</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>56991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>87556</t>
+          <t>96255</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71616</t>
+          <t>77610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>108344</t>
+          <t>117783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62453</t>
+          <t>37905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,27 +2350,27 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>40458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>29205</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73850</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>324605</t>
+          <t>363529</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>295516</t>
+          <t>341730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>343833</t>
+          <t>383827</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>357540</t>
+          <t>396872</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>342861</t>
+          <t>380013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>369523</t>
+          <t>411604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>682144</t>
+          <t>760401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>649490</t>
+          <t>733472</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>704002</t>
+          <t>783580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,36%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24295</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>40547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>29187</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>26406</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>53482</t>
+          <t>62281</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>47850</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>68122</t>
+          <t>80497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>422315</t>
+          <t>468731</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>422315</t>
+          <t>468731</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>422315</t>
+          <t>468731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>444161</t>
+          <t>494384</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>444161</t>
+          <t>494384</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>444161</t>
+          <t>494384</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>866475</t>
+          <t>963115</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>866475</t>
+          <t>963115</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>866475</t>
+          <t>963115</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>455994</t>
+          <t>232142</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>224645</t>
+          <t>199050</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1036912</t>
+          <t>268463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>210887</t>
+          <t>241610</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183237</t>
+          <t>214784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241175</t>
+          <t>269397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>666881</t>
+          <t>473752</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>427809</t>
+          <t>431721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1339538</t>
+          <t>521967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2884,102 +2884,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>21221</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>15246</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>29724</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>34743</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>24815</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>51625</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>19205</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>12809</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>28945</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>25396</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>17555</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>35874</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>83532</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51602</t>
+          <t>66239</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>107771</t>
+          <t>104096</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>57357</t>
+          <t>59061</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44034</t>
+          <t>47197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78889</t>
+          <t>74344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>130805</t>
+          <t>142593</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>121140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>165848</t>
+          <t>169309</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1672796</t>
+          <t>1852568</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1160705</t>
+          <t>1801126</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1877281</t>
+          <t>1896793</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1705214</t>
+          <t>1803249</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1663641</t>
+          <t>1766459</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1757144</t>
+          <t>1839968</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3378011</t>
+          <t>3655817</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2778103</t>
+          <t>3596694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3595914</t>
+          <t>3711567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>164879</t>
+          <t>173251</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>148492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>197182</t>
+          <t>207658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>178384</t>
+          <t>198524</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>154327</t>
+          <t>174703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>206361</t>
+          <t>223406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>343263</t>
+          <t>371775</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284834</t>
+          <t>335248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>386958</t>
+          <t>410451</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2373308</t>
+          <t>2355016</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2373308</t>
+          <t>2355016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2373308</t>
+          <t>2355016</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2171048</t>
+          <t>2323664</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2171048</t>
+          <t>2323664</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2171048</t>
+          <t>2323664</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4544357</t>
+          <t>4678680</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4544357</t>
+          <t>4678680</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4544357</t>
+          <t>4678680</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
